--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="供应商数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>供应商编号</t>
   </si>
@@ -74,6 +74,9 @@
     <t>联系人电话</t>
   </si>
   <si>
+    <t>外部平台编号</t>
+  </si>
+  <si>
     <t>采购次数</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
   </si>
   <si>
     <t>{.contactTelNumber}</t>
+  </si>
+  <si>
+    <t>{.voucherNo}</t>
   </si>
   <si>
     <t>{.purchasesCount}</t>
@@ -177,7 +183,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -190,13 +196,6 @@
       <sz val="13"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -673,151 +672,151 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -828,7 +827,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1364,7 +1363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -1373,15 +1372,15 @@
     <col min="7" max="10" width="10" customWidth="1"/>
     <col min="11" max="12" width="30" customWidth="1"/>
     <col min="13" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="10" customWidth="1"/>
+    <col min="15" max="16" width="20" customWidth="1"/>
+    <col min="17" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="20" customWidth="1"/>
+    <col min="24" max="24" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:23">
+    <row r="1" ht="30" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1451,76 +1450,82 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -74,27 +74,27 @@
     <t>联系人电话</t>
   </si>
   <si>
+    <t>采购次数</t>
+  </si>
+  <si>
+    <t>退货率</t>
+  </si>
+  <si>
+    <t>延期率</t>
+  </si>
+  <si>
+    <t>次品率</t>
+  </si>
+  <si>
+    <t>审核人（最新）</t>
+  </si>
+  <si>
+    <t>审核完成时间</t>
+  </si>
+  <si>
     <t>外部平台编号</t>
   </si>
   <si>
-    <t>采购次数</t>
-  </si>
-  <si>
-    <t>退货率</t>
-  </si>
-  <si>
-    <t>延期率</t>
-  </si>
-  <si>
-    <t>次品率</t>
-  </si>
-  <si>
-    <t>审核人（最新）</t>
-  </si>
-  <si>
-    <t>审核完成时间</t>
-  </si>
-  <si>
     <t>创建时间</t>
   </si>
   <si>
@@ -146,25 +146,25 @@
     <t>{.contactTelNumber}</t>
   </si>
   <si>
+    <t>{.purchasesCount}</t>
+  </si>
+  <si>
+    <t>{.rejectRate}</t>
+  </si>
+  <si>
+    <t>{.delayRate}</t>
+  </si>
+  <si>
+    <t>{.defectiveRate}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
+  </si>
+  <si>
     <t>{.voucherNo}</t>
-  </si>
-  <si>
-    <t>{.purchasesCount}</t>
-  </si>
-  <si>
-    <t>{.rejectRate}</t>
-  </si>
-  <si>
-    <t>{.delayRate}</t>
-  </si>
-  <si>
-    <t>{.defectiveRate}</t>
-  </si>
-  <si>
-    <t>{.approveUserName}</t>
-  </si>
-  <si>
-    <t>{.approveTime}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1372,11 +1372,11 @@
     <col min="7" max="10" width="10" customWidth="1"/>
     <col min="11" max="12" width="30" customWidth="1"/>
     <col min="13" max="14" width="10" customWidth="1"/>
-    <col min="15" max="16" width="20" customWidth="1"/>
-    <col min="17" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="20" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="23" width="20" customWidth="1"/>
     <col min="24" max="24" width="10" customWidth="1"/>
   </cols>
   <sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>供应商编号</t>
   </si>
   <si>
+    <t>供应商代码</t>
+  </si>
+  <si>
     <t>供应商名称</t>
   </si>
   <si>
@@ -47,6 +50,21 @@
     <t>供应商分类</t>
   </si>
   <si>
+    <t>工厂所在地</t>
+  </si>
+  <si>
+    <t>公司注册资金（万）</t>
+  </si>
+  <si>
+    <t>供应商属性</t>
+  </si>
+  <si>
+    <t>供应商品类</t>
+  </si>
+  <si>
+    <t>体系认证</t>
+  </si>
+  <si>
     <t>启用状态</t>
   </si>
   <si>
@@ -74,18 +92,6 @@
     <t>联系人电话</t>
   </si>
   <si>
-    <t>采购次数</t>
-  </si>
-  <si>
-    <t>退货率</t>
-  </si>
-  <si>
-    <t>延期率</t>
-  </si>
-  <si>
-    <t>次品率</t>
-  </si>
-  <si>
     <t>审核人（最新）</t>
   </si>
   <si>
@@ -104,6 +110,9 @@
     <t>{.code}</t>
   </si>
   <si>
+    <t>{.identificationCode}</t>
+  </si>
+  <si>
     <t>{.name}</t>
   </si>
   <si>
@@ -119,6 +128,21 @@
     <t>{.categoryName}</t>
   </si>
   <si>
+    <t>{.plantAddrNames}</t>
+  </si>
+  <si>
+    <t>{.registeredCapital}</t>
+  </si>
+  <si>
+    <t>{.propertyNames}</t>
+  </si>
+  <si>
+    <t>{.productCategoryNames}</t>
+  </si>
+  <si>
+    <t>{.certificateNames}</t>
+  </si>
+  <si>
     <t>{.enableStatus}</t>
   </si>
   <si>
@@ -144,18 +168,6 @@
   </si>
   <si>
     <t>{.contactTelNumber}</t>
-  </si>
-  <si>
-    <t>{.purchasesCount}</t>
-  </si>
-  <si>
-    <t>{.rejectRate}</t>
-  </si>
-  <si>
-    <t>{.delayRate}</t>
-  </si>
-  <si>
-    <t>{.defectiveRate}</t>
   </si>
   <si>
     <t>{.approveUserName}</t>
@@ -1363,24 +1375,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="20" customWidth="1"/>
-    <col min="7" max="10" width="10" customWidth="1"/>
-    <col min="11" max="12" width="30" customWidth="1"/>
-    <col min="13" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
-    <col min="22" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="10" customWidth="1"/>
+    <col min="1" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="20" customWidth="1"/>
+    <col min="11" max="12" width="22.125" customWidth="1"/>
+    <col min="13" max="16" width="10" customWidth="1"/>
+    <col min="17" max="18" width="30" customWidth="1"/>
+    <col min="19" max="20" width="10" customWidth="1"/>
+    <col min="21" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
+    <col min="24" max="25" width="20" customWidth="1"/>
+    <col min="26" max="26" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:24">
+    <row r="1" ht="30" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1453,79 +1464,91 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:26">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -164,10 +164,10 @@
     <t>{.purchaseUserName}</t>
   </si>
   <si>
-    <t>{.contactPerson}</t>
-  </si>
-  <si>
-    <t>{.contactTelNumber}</t>
+    <t>{.person}</t>
+  </si>
+  <si>
+    <t>{.telNumber}</t>
   </si>
   <si>
     <t>{.approveUserName}</t>
@@ -1384,7 +1384,8 @@
     <col min="11" max="12" width="22.125" customWidth="1"/>
     <col min="13" max="16" width="10" customWidth="1"/>
     <col min="17" max="18" width="30" customWidth="1"/>
-    <col min="19" max="20" width="10" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="16.125" customWidth="1"/>
     <col min="21" max="22" width="20" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
     <col min="24" max="25" width="20" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>供应商编号</t>
   </si>
@@ -59,7 +59,10 @@
     <t>供应商属性</t>
   </si>
   <si>
-    <t>供应商品类</t>
+    <t>产品品类</t>
+  </si>
+  <si>
+    <t>应用分类</t>
   </si>
   <si>
     <t>体系认证</t>
@@ -138,6 +141,9 @@
   </si>
   <si>
     <t>{.productCategoryNames}</t>
+  </si>
+  <si>
+    <t>{.applicationCategoryNames}</t>
   </si>
   <si>
     <t>{.certificateNames}</t>
@@ -1375,24 +1381,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="10" width="20" customWidth="1"/>
-    <col min="11" max="12" width="22.125" customWidth="1"/>
-    <col min="13" max="16" width="10" customWidth="1"/>
-    <col min="17" max="18" width="30" customWidth="1"/>
-    <col min="19" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="16.125" customWidth="1"/>
-    <col min="21" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="25" width="20" customWidth="1"/>
-    <col min="26" max="26" width="10" customWidth="1"/>
+    <col min="11" max="13" width="22.125" customWidth="1"/>
+    <col min="14" max="17" width="10" customWidth="1"/>
+    <col min="18" max="19" width="30" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="16.125" customWidth="1"/>
+    <col min="22" max="23" width="20" customWidth="1"/>
+    <col min="24" max="24" width="10" customWidth="1"/>
+    <col min="25" max="26" width="20" customWidth="1"/>
+    <col min="27" max="27" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:26">
+    <row r="1" ht="30" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1471,85 +1477,91 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>供应商编号</t>
   </si>
@@ -86,7 +86,10 @@
     <t>付款条件</t>
   </si>
   <si>
-    <t>采购员</t>
+    <t>采购开发员</t>
+  </si>
+  <si>
+    <t>采购跟单员</t>
   </si>
   <si>
     <t>联系人</t>
@@ -168,6 +171,9 @@
   </si>
   <si>
     <t>{.purchaseUserName}</t>
+  </si>
+  <si>
+    <t>{.poFollowerName}</t>
   </si>
   <si>
     <t>{.person}</t>
@@ -1381,7 +1387,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -1390,15 +1396,15 @@
     <col min="11" max="13" width="22.125" customWidth="1"/>
     <col min="14" max="17" width="10" customWidth="1"/>
     <col min="18" max="19" width="30" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="16.125" customWidth="1"/>
-    <col min="22" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="10" customWidth="1"/>
-    <col min="25" max="26" width="20" customWidth="1"/>
-    <col min="27" max="27" width="10" customWidth="1"/>
+    <col min="20" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="16.125" customWidth="1"/>
+    <col min="23" max="24" width="20" customWidth="1"/>
+    <col min="25" max="25" width="10" customWidth="1"/>
+    <col min="26" max="27" width="20" customWidth="1"/>
+    <col min="28" max="28" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:27">
+    <row r="1" ht="30" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1480,88 +1486,94 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/supplierExport.xlsx
@@ -27,110 +27,140 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
-  <si>
-    <t>供应商编号</t>
-  </si>
-  <si>
-    <t>供应商代码</t>
-  </si>
-  <si>
-    <t>供应商名称</t>
-  </si>
-  <si>
-    <t>单据状态</t>
-  </si>
-  <si>
-    <t>供应商阶段</t>
-  </si>
-  <si>
-    <t>供应商等级</t>
-  </si>
-  <si>
-    <t>供应商分类</t>
-  </si>
-  <si>
-    <t>工厂所在地</t>
-  </si>
-  <si>
-    <t>公司注册资金（万）</t>
-  </si>
-  <si>
-    <t>供应商属性</t>
-  </si>
-  <si>
-    <t>产品品类</t>
-  </si>
-  <si>
-    <t>应用分类</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+  <si>
+    <t>*供应商名称</t>
+  </si>
+  <si>
+    <t>*供应商等级</t>
+  </si>
+  <si>
+    <t>采购开发员</t>
+  </si>
+  <si>
+    <t>采购跟单员</t>
+  </si>
+  <si>
+    <t>公司地址</t>
+  </si>
+  <si>
+    <t>公司网址</t>
+  </si>
+  <si>
+    <t>*供应商状态</t>
+  </si>
+  <si>
+    <t>*结算方式</t>
+  </si>
+  <si>
+    <t>*结算币种</t>
+  </si>
+  <si>
+    <t>*供应商分类</t>
+  </si>
+  <si>
+    <t>*工厂所在地</t>
+  </si>
+  <si>
+    <t>*公司注册资金（万）</t>
+  </si>
+  <si>
+    <t>*供应商属性</t>
+  </si>
+  <si>
+    <t>*产品分类-二级分类</t>
+  </si>
+  <si>
+    <t>*应用分类</t>
+  </si>
+  <si>
+    <t>*付款条件</t>
+  </si>
+  <si>
+    <t>税率（%）</t>
   </si>
   <si>
     <t>体系认证</t>
   </si>
   <si>
-    <t>启用状态</t>
-  </si>
-  <si>
-    <t>SRM协同</t>
-  </si>
-  <si>
-    <t>订单接受规则</t>
-  </si>
-  <si>
-    <t>退货确认规则</t>
-  </si>
-  <si>
-    <t>结算方式</t>
-  </si>
-  <si>
-    <t>付款条件</t>
-  </si>
-  <si>
-    <t>采购开发员</t>
-  </si>
-  <si>
-    <t>采购跟单员</t>
-  </si>
-  <si>
     <t>联系人</t>
   </si>
   <si>
-    <t>联系人电话</t>
-  </si>
-  <si>
-    <t>审核人（最新）</t>
-  </si>
-  <si>
-    <t>审核完成时间</t>
-  </si>
-  <si>
-    <t>外部平台编号</t>
-  </si>
-  <si>
-    <t>创建时间</t>
-  </si>
-  <si>
-    <t>创建人</t>
-  </si>
-  <si>
-    <t>{.code}</t>
-  </si>
-  <si>
-    <t>{.identificationCode}</t>
+    <t>职务</t>
+  </si>
+  <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>默认联系人</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>联系人备注</t>
+  </si>
+  <si>
+    <t>账户名称</t>
+  </si>
+  <si>
+    <t>银行名称</t>
+  </si>
+  <si>
+    <t>开户行支行</t>
+  </si>
+  <si>
+    <t>银行账号</t>
+  </si>
+  <si>
+    <t>支付方式</t>
+  </si>
+  <si>
+    <t>账户备注</t>
+  </si>
+  <si>
+    <t>资质名称</t>
+  </si>
+  <si>
+    <t>资质有效期起</t>
+  </si>
+  <si>
+    <t>资质有效期止</t>
+  </si>
+  <si>
+    <t>资质备注</t>
   </si>
   <si>
     <t>{.name}</t>
   </si>
   <si>
-    <t>{.approveStatusName}</t>
-  </si>
-  <si>
-    <t>{.phaseName}</t>
-  </si>
-  <si>
     <t>{.gradeName}</t>
   </si>
   <si>
+    <t>{.purchaseUserName}</t>
+  </si>
+  <si>
+    <t>{.poFollowerName}</t>
+  </si>
+  <si>
+    <t>{.companyAddress}</t>
+  </si>
+  <si>
+    <t>{.companyWebsite}</t>
+  </si>
+  <si>
+    <t>{.enableStatus}</t>
+  </si>
+  <si>
+    <t>{.payMethodName}</t>
+  </si>
+  <si>
+    <t>{.payCurrencyName}</t>
+  </si>
+  <si>
     <t>{.categoryName}</t>
   </si>
   <si>
@@ -149,52 +179,64 @@
     <t>{.applicationCategoryNames}</t>
   </si>
   <si>
+    <t>{.paymentConditionName}</t>
+  </si>
+  <si>
+    <t>{.taxRate}</t>
+  </si>
+  <si>
     <t>{.certificateNames}</t>
   </si>
   <si>
-    <t>{.enableStatus}</t>
-  </si>
-  <si>
-    <t>{.srmDisabled}</t>
-  </si>
-  <si>
-    <t>{.orderAcceptRule}</t>
-  </si>
-  <si>
-    <t>{.returnConfirmRule}</t>
-  </si>
-  <si>
-    <t>{.payMethodName}</t>
-  </si>
-  <si>
-    <t>{.paymentConditionName}</t>
-  </si>
-  <si>
-    <t>{.purchaseUserName}</t>
-  </si>
-  <si>
-    <t>{.poFollowerName}</t>
-  </si>
-  <si>
     <t>{.person}</t>
   </si>
   <si>
+    <t>{.position}</t>
+  </si>
+  <si>
     <t>{.telNumber}</t>
   </si>
   <si>
-    <t>{.approveUserName}</t>
-  </si>
-  <si>
-    <t>{.approveTime}</t>
-  </si>
-  <si>
-    <t>{.voucherNo}</t>
-  </si>
-  <si>
-    <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>{.createUserName}</t>
+    <t>{.email}</t>
+  </si>
+  <si>
+    <t>{.contactIsDefaultName}</t>
+  </si>
+  <si>
+    <t>{.contactDisabledName}</t>
+  </si>
+  <si>
+    <t>{.contactRemark}</t>
+  </si>
+  <si>
+    <t>{.payee}</t>
+  </si>
+  <si>
+    <t>{.bankName}</t>
+  </si>
+  <si>
+    <t>{.bankSubbranch}</t>
+  </si>
+  <si>
+    <t>{.bankAccount}</t>
+  </si>
+  <si>
+    <t>{.bankPayMethodName}</t>
+  </si>
+  <si>
+    <t>{.accountRemark}</t>
+  </si>
+  <si>
+    <t>{.credentialName}</t>
+  </si>
+  <si>
+    <t>{.effectiveDate}</t>
+  </si>
+  <si>
+    <t>{.expireDate}</t>
+  </si>
+  <si>
+    <t>{.credentialRemark}</t>
   </si>
 </sst>
 </file>
@@ -1387,24 +1429,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="10" width="20" customWidth="1"/>
-    <col min="11" max="13" width="22.125" customWidth="1"/>
-    <col min="14" max="17" width="10" customWidth="1"/>
-    <col min="18" max="19" width="30" customWidth="1"/>
-    <col min="20" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="16.125" customWidth="1"/>
-    <col min="23" max="24" width="20" customWidth="1"/>
-    <col min="25" max="25" width="10" customWidth="1"/>
-    <col min="26" max="27" width="20" customWidth="1"/>
-    <col min="28" max="28" width="10" customWidth="1"/>
+    <col min="4" max="9" width="21" customWidth="1"/>
+    <col min="10" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="23.5" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="22.125" customWidth="1"/>
+    <col min="15" max="15" width="25.625" customWidth="1"/>
+    <col min="16" max="18" width="22.125" customWidth="1"/>
+    <col min="19" max="22" width="16.125" customWidth="1"/>
+    <col min="23" max="35" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:28">
+    <row r="1" ht="15" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1489,91 +1529,133 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:35">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
